--- a/report_forms/048_virtual_assistant_end_of_day_report_form--report_forms.xlsx
+++ b/report_forms/048_virtual_assistant_end_of_day_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>what_did_you_achieve</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First page</t>
+          <t>What did you accomplish today?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>end_of_day_report</t>
+          <t>biggest_challenges</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>end_of_day_report</t>
+          <t>What were the biggest challenges you faced?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>end_of_day_report</t>
+          <t>what_did_you_learn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>end_of_day_report</t>
+          <t>What did you learn today?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>did_anything_different</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>What did you do differently than usual?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>greatest_success</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>What was the most significant success you achieved?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>what_didnt_go_as_planned</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>What didn't go as planned?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>start_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>What time did you start working?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>finish_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What time did you finish work?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>what_did_you_do</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>did_you_do_anything</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>what_didnt_you_do</t>
+          <t>What did you do today?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>didnt_do_anything</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>What did you not do today?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date_of_report</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Date of the report</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>time_of_report</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Time of the report</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>report_what</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>What would you like to report?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>accomplished_goals</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>How did you accomplish your goals today?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,67 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>anything_else</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Would you like to report on anything else?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>what_would_you_like_to_report</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -983,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1011,204 +965,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>report_what_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>nothing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Nothing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>report_what_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>something</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Something</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>report_what_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>everything</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Everything</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>anything_else_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>nothing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Nothing</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>anything_else_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_0,_'label':_'nothing'}</t>
+          <t>something</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 0, 'label': 'Nothing'}</t>
+          <t>Something</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>anything_else_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'something'}</t>
+          <t>everything</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Something'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'everything'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Everything'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_0,_'label':_'nothing'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 0, 'label': 'Nothing'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'something'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Something'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'everything'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Everything'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_0,_'label':_'something'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 0, 'label': 'Something'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'everything'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Everything'}</t>
+          <t>Everything</t>
         </is>
       </c>
     </row>
